--- a/data_extactor/batch_10_fa/trimmed/batch_0074_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0074_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | مکانیک | مدیریت و امور اداری | ریاضیات | ایمنی و امنیت عمومی | تولید و فرآوری</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | مدیریت و اداره | ریاضیات | ایمنی و امنیت عمومی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استحکام تنه | انعطاف‌پذیری کششی | حساسیت به مسئله | دید نزدیک | استحکام ایستا | چابکی دستی | ثبات دست و بازو</t>
+          <t>قدرت تنه | انعطاف‌پذیری دامنه حرکت | حساسیت به مسئله | بینایی نزدیک | قدرت ایستا | مهارت دستی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>نصابان صفحات گچی و تایل‌های سقفی | کارگران کمکی لوله‌گذاران، لوله‌کش‌ها و نصابان لوله و اتصالات | عایق‌کاران کف، سقف و دیوار | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | عایق‌کاران و نصابان پوشش‌های سقفی | کارگران ورق‌کاری فلزی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی</t>
+          <t>نصابان دیوار کاذب و تایل سقف | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | عایق‌کاران کف، سقف و دیوار | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | عایق‌کاران و نصابان پوشش‌های سقفی | کارگران ورق‌کاری فلزی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ساخت‌وساز و ابنیه</t>
+          <t>خدمات مشتری و شخصی | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | چابکی دستی | استحکام تنه | تشخیص رنگ‌ها | تعادل کلی بدن | هماهنگی چنداندامی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | مهارت دستی | قدرت تنه | تشخیص رنگ بصری | تعادل کلی بدن | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>نجاران | کارگران ساده ساختمانی | پرداخت‌کاران و رنگ‌کاران مصنوعات چوبی | کارگران کمکی نقاشان، نصابان کاغذ دیواری و گچ‌کاران | کارگران رنگ‌کاری، پوشش‌دهی و تزیین | نصابان کاغذ دیواری | سفیدکاران و گچ‌کاران نما</t>
+          <t>نجاران و درودگران | کارگران ساختمانی | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | نصابان کاغذ دیواری | سفیدکاران و گچ‌کاران نما</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ساخت‌وساز و ابنیه | ریاضیات | مکانیک | ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | ریاضیات | مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی دستی | ثبات دست و بازو | انعطاف‌پذیری کششی | هماهنگی چنداندامی | چابکی انگشتان | دقت کنترل</t>
+          <t>بینایی نزدیک | مهارت دستی | ثبات دست و بازو | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | مهارت انگشتان | دقت کنترل</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>نجاران | نصابان موکت و کف‌پوش نرم | نصابان صفحات گچی و تایل‌های سقفی | نصابان کف‌پوش، به‌جز موکت، چوب و کاشی سخت | کارگران کمکی نقاشان، نصابان کاغذ دیواری و گچ‌کاران | نقاشان ساختمان و تاسیسات | سفیدکاران و گچ‌کاران نما</t>
+          <t>نجاران و درودگران | موکت‌کاران و نصابان فرش | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | نقاشان ساختمان و تاسیسات | سفیدکاران و گچ‌کاران نما</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | ایمنی و امنیت عمومی</t>
+          <t>ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دقت کنترل | ثبات دست و بازو | درک شفاهی | استحکام ایستا | ادراک عمق | دید نزدیک | استحکام تنه</t>
+          <t>دقت کنترل | ثبات دست و بازو | درک شفاهی | قدرت ایستا | درک عمق | بینایی نزدیک | قدرت تنه</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساده ساختمانی | نصابان و تعمیرکاران خطوط انتقال نیرو | کارگران کمکی لوله‌گذاران، لوله‌کش‌ها و نصابان لوله و اتصالات | اپراتورهای ماشین‌آلات آسفالت‌کاری و تراکم | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | سرویس‌کاران سپتیک‌تانک و لایروبان مجاری فاضلاب</t>
+          <t>بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | مکانیک | طراحی | ریاضیات | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | طراحی | ریاضیات | خدمات مشتری و شخصی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | چابکی انگشتان | دید نزدیک | چابکی دستی | استدلال قیاسی | استحکام تنه | تجسم فضایی</t>
+          <t>حساسیت به مسئله | مهارت انگشتان | بینایی نزدیک | مهارت دستی | استدلال قیاسی | قدرت تنه | تجسم</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>دیگ‌سازان صنعتی | نصابان و تعمیرکاران کنترل‌کننده‌ها و شیرآلات، به‌جز درب‌های مکانیکی | مکانیک‌ها و نصابان سیستم‌های سرمایشی، گرمایشی و تهویه مطبوع | کارگران کمکی لوله‌گذاران، لوله‌کش‌ها و نصابان لوله و اتصالات | کارگران تعمیرات و نگهداری عمومی | لوله‌گذاران خطوط انتقال | تکنسین‌ها و اپراتورهای دیگ بخار و موتورخانه</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کارگران عمومی تعمیرات و نگهداری تاسیسات | لوله‌گذاران خطوط انتقال | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | یادگیری فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | ساخت‌وساز و ابنیه | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | طراحی | ایمنی و امنیت عمومی | رایانه و الکترونیک</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مهندسی و فناوری | طراحی | ایمنی و امنیت عمومی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | انعطاف‌پذیری کششی | حساسیت به مسئله | درک کتبی | ثبات دست و بازو | چابکی دستی</t>
+          <t>درک شفاهی | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | حساسیت به مسئله | درک کتبی | ثبات دست و بازو | مهارت دستی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان برق | مکانیک‌ها و نصابان سیستم‌های سرمایشی، گرمایشی و تهویه مطبوع | کارگران کمکی لوله‌گذاران، لوله‌کش‌ها و نصابان لوله و اتصالات | عایق‌کاران تاسیسات مکانیکی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک</t>
+          <t>مهندسان برق | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | عایق‌کاران تاسیسات مکانیکی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | مدیریت و امور اداری | طراحی | زبان انگلیسی | خدمات مشتریان و خدمات فردی</t>
+          <t>ساختمان و ساخت‌وساز | مدیریت و اداره | طراحی | زبان انگلیسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | چابکی دستی | انعطاف‌پذیری کششی | استحکام تنه | استحکام ایستا | استقامت بدنی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت دستی | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | استقامت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بناها و آجرچین‌ها | بتن‌ریزان و پرداخت‌کاران بتن | نصابان صفحات گچی و تایل‌های سقفی | کارگران کمکی بناها، آجرچین‌ها، سنگ‌کاران و کاشی‌کاران | کارگران کمکی نقاشان، نصابان کاغذ دیواری و گچ‌کاران | نقاشان ساختمان و تاسیسات | بتونه‌کاران و درزگیران درای‌وال</t>
+          <t>بنایان و سفت‌کاران ساختمان | بتن‌ریزان و پرداخت‌کاران بتن | نصابان دیوار کاذب و تایل سقف | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | نقاشان ساختمان و تاسیسات | بتونه‌کاران و درزگیران دیوار کاذب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | ریاضیات | مدیریت و امور اداری | طراحی | زبان انگلیسی | مهندسی و فناوری</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | مدیریت و اداره | طراحی | زبان انگلیسی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استحکام تنه | استحکام ایستا | هماهنگی چنداندامی | چابکی دستی | انعطاف‌پذیری کششی | ثبات دست و بازو | استقامت بدنی</t>
+          <t>قدرت تنه | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | استقامت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بناها و آجرچین‌ها | نجاران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساده ساختمانی | کارگران کمکی بناها، آجرچین‌ها، سنگ‌کاران و کاشی‌کاران | اسکلت‌سازان فلزی و کارگران فولاد ساختمانی | سازندگان و نصابان سازه‌های فلزی</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ساخت‌وساز و ابنیه | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | ریاضیات | طراحی | مکانیک</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | ریاضیات | طراحی | مکانیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>تعادل کلی بدن | انعطاف‌پذیری کششی | استحکام تنه | حساسیت به مسئله | دید نزدیک | هماهنگی چنداندامی | استقامت بدنی</t>
+          <t>تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت تنه | حساسیت به مسئله | بینایی نزدیک | هماهنگی چند عضو | استقامت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بناها و آجرچین‌ها | نجاران | نصابان صفحات گچی و تایل‌های سقفی | کارگران کمکی بناها، آجرچین‌ها، سنگ‌کاران و کاشی‌کاران | کارگران کمکی نصابان پوشش‌های سقفی | عایق‌کاران کف، سقف و دیوار | کارگران ورق‌کاری فلزی</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | نصابان دیوار کاذب و تایل سقف | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌ایزوگام‌کاران و کمک‌عایق‌کاران سقف | عایق‌کاران کف، سقف و دیوار | کارگران ورق‌کاری فلزی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | تفکر انتقادی | ریاضیات | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | درک مطلب | تفکر انتقادی | ریاضیات | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | ساخت‌وساز و ابنیه | ریاضیات | طراحی | تولید و فرآوری | مهندسی و فناوری</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | ریاضیات | طراحی | تولید و فرآوری | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>تجسم فضایی | دید نزدیک | هماهنگی چنداندامی | چابکی دستی | ثبات دست و بازو | چابکی انگشتان | استحکام تنه</t>
+          <t>تجسم | بینایی نزدیک | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | مهارت انگشتان | قدرت تنه</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دیگ‌سازان صنعتی | مونتاژکاران موتور و ماشین‌آلات صنعتی | مکانیک‌های ماشین‌آلات صنعتی | عایق‌کاران تاسیسات مکانیکی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | اسکلت‌سازان فلزی و کارگران فولاد ساختمانی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های جوشکاری، لحیم‌کاری و بریزینگ</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | عایق‌کاران تاسیسات مکانیکی | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | اسکلت‌سازان و نصابان سازه‌های فولادی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
